--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 85 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 82 clubs short</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6726,8 +6726,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -6994,7 +6994,7 @@
         <v>2</v>
       </c>
       <c r="R65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" s="9" t="n">
         <v>1</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11382,8 +11382,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15232,8 +15232,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P150" s="9" t="n">
-        <v>3</v>
+      <c r="P150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>1</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -16620,8 +16620,8 @@
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="9" t="n">
-        <v>0</v>
+      <c r="Z164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA164" s="10" t="n">
         <v>1</v>
@@ -18727,7 +18727,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -18991,7 +18991,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19255,7 +19255,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -19321,7 +19321,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 82 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 76 clubs short</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1003,8 +1003,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1470,8 +1470,8 @@
       <c r="S8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="9" t="n">
-        <v>0</v>
+      <c r="T8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U8" s="9" t="n">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -2723,7 +2723,7 @@
         <v>2</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>0</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>5</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="P26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="9" t="n">
         <v>0</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5641,8 +5641,8 @@
       <c r="S51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T51" s="9" t="n">
-        <v>0</v>
+      <c r="T51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U51" s="9" t="n">
         <v>0</v>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="9" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
         <v>2</v>
       </c>
       <c r="R76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" s="9" t="n">
         <v>1</v>
@@ -8084,8 +8084,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9712,14 +9712,14 @@
       <c r="R93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S93" s="9" t="n">
-        <v>1</v>
+      <c r="S93" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T93" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U93" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V93" s="10" t="n">
         <v>4</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9900,8 +9900,8 @@
       <c r="P95" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q95" s="9" t="n">
-        <v>1</v>
+      <c r="Q95" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11950,7 +11950,7 @@
         <v>1</v>
       </c>
       <c r="U116" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V116" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14195,8 +14195,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14265,8 +14265,8 @@
       <c r="P140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" s="9" t="n">
-        <v>1</v>
+      <c r="Q140" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -18364,7 +18364,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18397,7 +18397,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18661,7 +18661,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18826,7 +18826,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -18892,7 +18892,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -18925,13 +18925,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -19057,7 +19057,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -19189,7 +19189,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 76 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -906,8 +906,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1682,8 +1682,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2555,8 +2555,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -2652,8 +2652,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="9" t="n">
         <v>0</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2846,8 +2846,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="9" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3234,8 +3234,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="9" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3331,8 +3331,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4204,8 +4204,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4495,8 +4495,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4883,8 +4883,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -5368,8 +5368,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="9" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5659,8 +5659,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6323,8 +6323,8 @@
       <c r="T58" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U58" s="9" t="n">
-        <v>0</v>
+      <c r="U58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V58" s="9" t="n">
         <v>0</v>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7399,8 +7399,8 @@
       <c r="W69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X69" s="9" t="n">
-        <v>0</v>
+      <c r="X69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7890,8 +7890,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -8175,8 +8175,8 @@
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X77" s="9" t="n">
-        <v>3</v>
+      <c r="X77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8957,8 +8957,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -9036,8 +9036,8 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q93" s="10" t="n">
         <v>2</v>
@@ -9725,7 +9725,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>6</v>
@@ -9904,7 +9904,7 @@
         <v>2</v>
       </c>
       <c r="R95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" s="9" t="n">
         <v>0</v>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11091,8 +11091,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -11576,8 +11576,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11867,8 +11867,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12546,8 +12546,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13613,8 +13613,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -13931,7 +13931,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14001,8 +14001,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14804,7 +14804,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14874,8 +14874,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14945,19 +14945,19 @@
         <v>1</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V147" s="10" t="n">
         <v>4</v>
@@ -14971,8 +14971,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="9" t="n">
         <v>0</v>
@@ -15430,13 +15430,13 @@
         <v>1</v>
       </c>
       <c r="Q152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" s="10" t="n">
         <v>1</v>
@@ -15718,7 +15718,7 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q155" s="9" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15844,8 +15844,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16505,8 +16505,8 @@
       <c r="S163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T163" s="9" t="n">
-        <v>0</v>
+      <c r="T163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U163" s="9" t="n">
         <v>0</v>
@@ -17079,7 +17079,7 @@
         <v>1</v>
       </c>
       <c r="Q169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R169" s="9" t="n">
         <v>0</v>
@@ -17326,7 +17326,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="V172" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
@@ -17396,8 +17396,8 @@
       <c r="Y172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z172" s="9" t="n">
-        <v>0</v>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA172" s="10" t="n">
         <v>1</v>
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -17590,8 +17590,8 @@
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="9" t="n">
-        <v>0</v>
+      <c r="Z174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
@@ -17617,7 +17617,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -17687,8 +17687,8 @@
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="9" t="n">
-        <v>0</v>
+      <c r="Z175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
@@ -18102,7 +18102,7 @@
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -18172,8 +18172,8 @@
       <c r="Y180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z180" s="9" t="n">
-        <v>0</v>
+      <c r="Z180" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA180" s="10" t="n">
         <v>1</v>
@@ -18364,7 +18364,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18397,7 +18397,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18430,7 +18430,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -18463,7 +18463,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18496,7 +18496,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18529,7 +18529,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -18562,7 +18562,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -18661,7 +18661,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18694,7 +18694,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18760,7 +18760,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18793,7 +18793,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18826,7 +18826,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -18859,7 +18859,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18991,7 +18991,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19024,7 +19024,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19090,7 +19090,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19156,7 +19156,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19222,7 +19222,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -19288,7 +19288,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -19321,7 +19321,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19387,7 +19387,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -19420,7 +19420,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$183</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 40 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA181"/>
+  <dimension ref="A1:AA183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1185,11 +1185,11 @@
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W5" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>5</v>
@@ -1238,17 +1238,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1432,17 +1432,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1820,17 +1820,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1864,11 +1864,11 @@
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="9" t="n">
-        <v>3</v>
+      <c r="V12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>7</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -1952,8 +1952,8 @@
       <c r="R13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="9" t="n">
-        <v>1</v>
+      <c r="S13" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T13" s="9" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>4</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2305,17 +2305,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2402,17 +2402,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3372,17 +3372,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>7</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -3857,17 +3857,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -3998,8 +3998,8 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>3</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4659,8 +4659,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P41" s="9" t="n">
-        <v>3</v>
+      <c r="P41" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Q41" s="10" t="n">
         <v>2</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -4871,8 +4871,8 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>3</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5453,8 +5453,8 @@
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>2</v>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,17 +5797,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -5894,17 +5894,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" s="9" t="n">
         <v>0</v>
@@ -6324,10 +6324,10 @@
         <v>1</v>
       </c>
       <c r="U58" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6714,11 +6714,11 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>2</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>6</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6811,11 +6811,11 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>3</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>5</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6961,17 +6961,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7252,17 +7252,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7587,8 +7587,8 @@
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>1</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7931,17 +7931,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8222,17 +8222,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -8557,11 +8557,11 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>2</v>
+      <c r="V81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>7</v>
@@ -8610,17 +8610,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -8754,8 +8754,8 @@
       <c r="V83" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W83" s="9" t="n">
-        <v>0</v>
+      <c r="W83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>5</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9095,17 +9095,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>6</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9818,11 +9818,11 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>3</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>5</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>1</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>4</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10259,17 +10259,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,17 +10744,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -10791,8 +10791,8 @@
       <c r="V104" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W104" s="9" t="n">
-        <v>2</v>
+      <c r="W104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>7</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11035,17 +11035,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11276,8 +11276,8 @@
       <c r="V109" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W109" s="9" t="n">
-        <v>2</v>
+      <c r="W109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11370,8 +11370,8 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>3</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12199,17 +12199,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>5</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -12826,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -12923,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13460,17 +13460,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13601,11 +13601,11 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>3</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>4</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>2</v>
       </c>
       <c r="R140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S140" s="10" t="n">
         <v>2</v>
@@ -14280,8 +14280,8 @@
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="9" t="n">
-        <v>2</v>
+      <c r="V140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14333,17 +14333,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14662,17 +14662,17 @@
       <c r="S144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="9" t="n">
-        <v>0</v>
+      <c r="T144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>0</v>
+      <c r="V144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>6</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14962,8 +14962,8 @@
       <c r="V147" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W147" s="9" t="n">
-        <v>0</v>
+      <c r="W147" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X147" s="10" t="n">
         <v>4</v>
@@ -15012,17 +15012,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>4</v>
       </c>
       <c r="W150" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>5</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -15541,8 +15541,8 @@
       <c r="U153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V153" s="9" t="n">
-        <v>3</v>
+      <c r="V153" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -15691,17 +15691,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="8" t="n">
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -15826,8 +15826,8 @@
       <c r="S156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T156" s="9" t="n">
-        <v>0</v>
+      <c r="T156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U156" s="9" t="n">
         <v>0</v>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -15929,11 +15929,11 @@
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V157" s="9" t="n">
-        <v>1</v>
+      <c r="V157" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W157" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X157" s="10" t="n">
         <v>4</v>
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -15982,17 +15982,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L158" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="8" t="n">
@@ -16026,8 +16026,8 @@
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V158" s="9" t="n">
-        <v>2</v>
+      <c r="V158" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16079,17 +16079,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16217,8 +16217,8 @@
       <c r="T160" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U160" s="9" t="n">
-        <v>0</v>
+      <c r="U160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V160" s="10" t="n">
         <v>4</v>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -16467,17 +16467,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -16855,13 +16855,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="V167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W167" s="9" t="n">
         <v>0</v>
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17146,13 +17146,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -17243,17 +17243,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-30</v>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
@@ -17326,7 +17326,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -17384,8 +17384,8 @@
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="9" t="n">
-        <v>2</v>
+      <c r="V172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -17534,17 +17534,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L174" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M174" s="8" t="n">
@@ -17617,7 +17617,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -17631,17 +17631,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M175" s="8" t="n">
@@ -17675,8 +17675,8 @@
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V175" s="9" t="n">
-        <v>1</v>
+      <c r="V175" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
@@ -17728,13 +17728,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -17900,15 +17900,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>4310072</v>
+        <v>28680785</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Epic Orators Advanced Toastmasters</t>
+          <t>Classy Ladies Of The World</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -17922,17 +17922,17 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K178" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L178" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M178" s="8" t="n">
@@ -17972,14 +17972,14 @@
       <c r="W178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X178" s="10" t="n">
-        <v>6</v>
+      <c r="X178" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="9" t="n">
-        <v>0</v>
+      <c r="Z178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA178" s="10" t="n">
         <v>1</v>
@@ -17997,15 +17997,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>9792</v>
+        <v>4310072</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Friendship Toastmasters</t>
+          <t>Epic Orators Advanced Toastmasters</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q179" s="9" t="n">
         <v>0</v>
@@ -18055,7 +18055,7 @@
         <v>0</v>
       </c>
       <c r="S179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T179" s="9" t="n">
         <v>0</v>
@@ -18064,19 +18064,19 @@
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X179" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" s="10" t="n">
-        <v>1</v>
+      <c r="Z179" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA179" s="10" t="n">
         <v>1</v>
@@ -18094,15 +18094,15 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>1426335</v>
+        <v>9792</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Second Mile Speakers</t>
+          <t>Friendship Toastmasters</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -18116,17 +18116,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M180" s="8" t="n">
@@ -18146,28 +18146,28 @@
         <v>1</v>
       </c>
       <c r="Q180" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R180" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T180" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T180" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U180" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V180" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W180" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X180" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y180" s="9" t="n">
         <v>0</v>
@@ -18191,93 +18191,287 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
+        <v>28680748</v>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>Panthers Toastmasters at GSU</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G181" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J181" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K181" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M181" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O181" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>1426335</v>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>Second Mile Speakers</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F182" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J182" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="K182" s="4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="L182" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M182" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O182" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P182" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q182" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U182" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W182" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X182" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y182" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA182" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="n">
         <v>28678129</v>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D183" s="4" t="inlineStr">
         <is>
           <t>Southside Leaders in Language</t>
         </is>
       </c>
-      <c r="E181" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G181" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H181" s="4" t="inlineStr">
+      <c r="E183" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G183" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
         <is>
           <t>Smedley</t>
         </is>
       </c>
-      <c r="I181" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J181" s="4" t="n">
+      <c r="I183" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J183" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K181" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L181" s="7" t="inlineStr">
+      <c r="K183" s="4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M181" s="8" t="n">
+      <c r="M183" s="8" t="n">
         <v>46387</v>
       </c>
-      <c r="N181" s="4" t="inlineStr">
+      <c r="N183" s="4" t="inlineStr">
         <is>
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O181" s="7" t="inlineStr">
+      <c r="O183" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X181" s="10" t="n">
+      <c r="P183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V183" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X183" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Y181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA181" s="9" t="n">
+      <c r="Y183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA181"/>
+  <autoFilter ref="A1:AA183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18364,7 +18558,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18379,7 +18573,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -18412,7 +18606,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -18430,7 +18624,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -18445,7 +18639,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -18478,7 +18672,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -18511,7 +18705,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -18544,7 +18738,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -18562,7 +18756,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18595,7 +18789,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -18610,7 +18804,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -18661,7 +18855,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18676,7 +18870,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -18727,7 +18921,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -18742,7 +18936,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -18775,7 +18969,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -18793,7 +18987,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18808,7 +19002,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -18826,7 +19020,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -18841,7 +19035,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -18859,7 +19053,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18874,7 +19068,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -18907,7 +19101,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -18925,7 +19119,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -18940,7 +19134,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -18958,7 +19152,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -18973,7 +19167,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -18991,7 +19185,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19006,7 +19200,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -19072,7 +19266,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -19105,7 +19299,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -19138,7 +19332,7 @@
         <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -19156,7 +19350,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19171,7 +19365,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -19189,7 +19383,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -19204,7 +19398,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -19222,7 +19416,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -19237,7 +19431,7 @@
         <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -19255,7 +19449,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -19288,7 +19482,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -19303,7 +19497,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -19321,13 +19515,13 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -19336,7 +19530,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -19369,7 +19563,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -19387,7 +19581,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -19402,7 +19596,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -19417,16 +19611,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -19435,7 +19629,7 @@
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1379,8 +1379,8 @@
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="9" t="n">
-        <v>3</v>
+      <c r="V7" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1432,17 +1432,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>4</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>6</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2446,8 +2446,8 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>3</v>
+      <c r="V18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3907,8 +3907,8 @@
       <c r="W33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X33" s="9" t="n">
-        <v>3</v>
+      <c r="X33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="X40" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y40" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" s="9" t="n">
         <v>0</v>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>1</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>1</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>6</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>6</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7966,8 +7966,8 @@
       <c r="R75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S75" s="9" t="n">
-        <v>1</v>
+      <c r="S75" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T75" s="10" t="n">
         <v>1</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>3</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-22</v>
+        <v>-15</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9415,8 +9415,8 @@
       <c r="P90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" s="9" t="n">
-        <v>1</v>
+      <c r="Q90" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9913,7 +9913,7 @@
         <v>1</v>
       </c>
       <c r="U95" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V95" s="9" t="n">
         <v>3</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10112,8 +10112,8 @@
       <c r="V97" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W97" s="9" t="n">
-        <v>3</v>
+      <c r="W97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>4</v>
@@ -10213,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L103" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11467,8 +11467,8 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>2</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12337,14 +12337,14 @@
       <c r="T120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U120" s="9" t="n">
-        <v>0</v>
+      <c r="U120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V120" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>7</v>
@@ -12444,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13557,17 +13557,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14650,8 +14650,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P144" s="9" t="n">
-        <v>2</v>
+      <c r="P144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>1</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15235,8 +15235,8 @@
       <c r="P150" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q150" s="9" t="n">
-        <v>1</v>
+      <c r="Q150" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>4</v>
       </c>
       <c r="W150" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>5</v>
@@ -15644,8 +15644,8 @@
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X154" s="9" t="n">
-        <v>1</v>
+      <c r="X154" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -16511,11 +16511,11 @@
       <c r="U163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="9" t="n">
-        <v>3</v>
+      <c r="V163" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X163" s="10" t="n">
         <v>4</v>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>0</v>
       </c>
       <c r="V169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W169" s="9" t="n">
         <v>0</v>
@@ -17173,7 +17173,7 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q170" s="9" t="n">
         <v>0</v>
@@ -17182,7 +17182,7 @@
         <v>0</v>
       </c>
       <c r="S170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T170" s="9" t="n">
         <v>0</v>
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>4</v>
       </c>
       <c r="W172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X172" s="10" t="n">
         <v>5</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -17609,15 +17609,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>28678876</v>
+        <v>28680748</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Technically Speaking</t>
+          <t>Panthers Toastmasters at GSU</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -17631,17 +17631,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L175" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M175" s="8" t="n">
@@ -17666,8 +17666,8 @@
       <c r="R175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S175" s="10" t="n">
-        <v>2</v>
+      <c r="S175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T175" s="9" t="n">
         <v>0</v>
@@ -17675,20 +17675,20 @@
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V175" s="10" t="n">
-        <v>4</v>
+      <c r="V175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X175" s="10" t="n">
-        <v>7</v>
+      <c r="X175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="10" t="n">
-        <v>1</v>
+      <c r="Z175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
@@ -17706,15 +17706,15 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>2490</v>
+        <v>28678876</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Tri-Cities Toastmasters Club</t>
+          <t>Technically Speaking</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -17728,10 +17728,10 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K176" s="4" t="n">
         <v>-1</v>
@@ -17757,29 +17757,29 @@
       <c r="P176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" s="10" t="n">
+      <c r="Q176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T176" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U176" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V176" s="9" t="n">
-        <v>3</v>
+      <c r="T176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X176" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y176" s="9" t="n">
         <v>0</v>
@@ -17799,19 +17799,19 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>7912182</v>
+        <v>2490</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Black Achievement Fund Toastmasters</t>
+          <t>Tri-Cities Toastmasters Club</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -17839,11 +17839,11 @@
         </is>
       </c>
       <c r="M177" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N177" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O177" s="7" t="inlineStr">
@@ -17854,8 +17854,8 @@
       <c r="P177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" s="9" t="n">
-        <v>0</v>
+      <c r="Q177" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>0</v>
@@ -17866,26 +17866,26 @@
       <c r="T177" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U177" s="9" t="n">
-        <v>0</v>
+      <c r="U177" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X177" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA177" s="9" t="n">
-        <v>0</v>
+      <c r="Z177" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA177" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -17900,11 +17900,11 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>28680785</v>
+        <v>7912182</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Classy Ladies Of The World</t>
+          <t>Black Achievement Fund Toastmasters</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
@@ -17922,25 +17922,25 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L178" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M178" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N178" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O178" s="7" t="inlineStr">
@@ -17960,8 +17960,8 @@
       <c r="S178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T178" s="9" t="n">
-        <v>0</v>
+      <c r="T178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U178" s="9" t="n">
         <v>0</v>
@@ -17972,17 +17972,17 @@
       <c r="W178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X178" s="9" t="n">
-        <v>0</v>
+      <c r="X178" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA178" s="10" t="n">
-        <v>1</v>
+      <c r="Z178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA178" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -17997,15 +17997,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>4310072</v>
+        <v>28680785</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Epic Orators Advanced Toastmasters</t>
+          <t>Classy Ladies Of The World</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18019,17 +18019,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K179" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L179" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
@@ -18064,19 +18064,19 @@
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X179" s="10" t="n">
-        <v>6</v>
+      <c r="X179" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" s="9" t="n">
-        <v>0</v>
+      <c r="Z179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA179" s="10" t="n">
         <v>1</v>
@@ -18094,15 +18094,15 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>9792</v>
+        <v>4310072</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Friendship Toastmasters</t>
+          <t>Epic Orators Advanced Toastmasters</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -18116,13 +18116,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -18143,16 +18143,16 @@
         </is>
       </c>
       <c r="P180" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q180" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R180" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S180" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T180" s="9" t="n">
         <v>0</v>
@@ -18167,13 +18167,13 @@
         <v>0</v>
       </c>
       <c r="X180" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z180" s="10" t="n">
-        <v>1</v>
+      <c r="Z180" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA180" s="10" t="n">
         <v>1</v>
@@ -18191,15 +18191,15 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>28680748</v>
+        <v>9792</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Panthers Toastmasters at GSU</t>
+          <t>Friendship Toastmasters</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -18213,17 +18213,17 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L181" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M181" s="8" t="n">
@@ -18240,16 +18240,16 @@
         </is>
       </c>
       <c r="P181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R181" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T181" s="9" t="n">
         <v>0</v>
@@ -18258,19 +18258,19 @@
         <v>0</v>
       </c>
       <c r="V181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X181" s="9" t="n">
-        <v>0</v>
+      <c r="X181" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z181" s="9" t="n">
-        <v>0</v>
+      <c r="Z181" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA181" s="10" t="n">
         <v>1</v>
@@ -18591,7 +18591,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18606,7 +18606,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -18657,7 +18657,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19086,7 +19086,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -19119,7 +19119,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -19167,7 +19167,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -19218,7 +19218,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19251,13 +19251,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -19365,7 +19365,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -19416,7 +19416,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -19449,13 +19449,13 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -19515,7 +19515,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -19578,16 +19578,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -19611,16 +19611,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -19629,7 +19629,7 @@
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/214/inyear.xlsx
+++ b/docs/d/214/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -1144,10 +1144,10 @@
         <v>24</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="9" t="n">
         <v>3</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2211,10 +2211,10 @@
         <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2402,17 +2402,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="X33" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q37" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5459,8 +5459,8 @@
       <c r="W49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X49" s="9" t="n">
-        <v>3</v>
+      <c r="X49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y49" s="9" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>6</v>
@@ -6964,10 +6964,10 @@
         <v>19</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>6</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7934,10 +7934,10 @@
         <v>18</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8266,8 +8266,8 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>3</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8363,8 +8363,8 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>3</v>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>4</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>1</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>5</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9039,8 +9039,8 @@
       <c r="T86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+      <c r="U86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>5</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9915,11 +9915,11 @@
       <c r="U95" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>3</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>6</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10192,13 +10192,13 @@
         <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" s="10" t="n">
         <v>1</v>
@@ -10206,8 +10206,8 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>3</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>2</v>
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10650,10 +10650,10 @@
         <v>20</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11085,8 +11085,8 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="9" t="n">
-        <v>2</v>
+      <c r="X107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-11</v>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11661,11 +11661,11 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W113" s="9" t="n">
-        <v>0</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W113" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X113" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>1</v>
@@ -12140,8 +12140,8 @@
       <c r="S118" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
@@ -12338,7 +12338,7 @@
         <v>1</v>
       </c>
       <c r="U120" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V120" s="10" t="n">
         <v>4</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12519,8 +12519,8 @@
       <c r="P122" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q122" s="9" t="n">
-        <v>1</v>
+      <c r="Q122" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -12687,10 +12687,10 @@
         <v>29</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -13407,8 +13407,8 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>3</v>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13892,11 +13892,11 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>0</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X136" s="9" t="n">
         <v>0</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14530,10 +14530,10 @@
         <v>2</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14671,8 +14671,8 @@
       <c r="V144" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W144" s="9" t="n">
-        <v>3</v>
+      <c r="W144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>6</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15435,8 +15435,8 @@
       <c r="R152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S152" s="9" t="n">
-        <v>1</v>
+      <c r="S152" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T152" s="10" t="n">
         <v>1</v>
@@ -15500,10 +15500,10 @@
         <v>21</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -15985,10 +15985,10 @@
         <v>18</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16082,10 +16082,10 @@
         <v>13</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16202,17 +16202,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P160" s="9" t="n">
+      <c r="P160" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q160" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q160" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160" s="10" t="n">
         <v>1</v>
@@ -16273,10 +16273,10 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K161" s="4" t="n">
         <v>-2</v>
@@ -16321,7 +16321,7 @@
         <v>4</v>
       </c>
       <c r="W161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X161" s="10" t="n">
         <v>4</v>
@@ -16420,8 +16420,8 @@
       <c r="W162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X162" s="9" t="n">
-        <v>1</v>
+      <c r="X162" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16496,8 +16496,8 @@
       <c r="P163" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q163" s="9" t="n">
-        <v>1</v>
+      <c r="Q163" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R163" s="9" t="n">
         <v>0</v>
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17052,10 +17052,10 @@
         <v>32</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -17243,17 +17243,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="L171" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
@@ -17287,8 +17287,8 @@
       <c r="U171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V171" s="9" t="n">
-        <v>0</v>
+      <c r="V171" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -17299,8 +17299,8 @@
       <c r="Y171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z171" s="9" t="n">
-        <v>0</v>
+      <c r="Z171" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA171" s="10" t="n">
         <v>1</v>
@@ -18216,10 +18216,10 @@
         <v>12</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>1</v>
       </c>
       <c r="Q182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" s="9" t="n">
         <v>0</v>
@@ -18407,13 +18407,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -18756,7 +18756,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -19020,7 +19020,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -19053,7 +19053,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19119,7 +19119,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -19200,7 +19200,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -19218,7 +19218,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19251,7 +19251,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -19284,7 +19284,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19317,7 +19317,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -19350,7 +19350,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19416,13 +19416,13 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -19449,7 +19449,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -19515,7 +19515,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -19548,7 +19548,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19563,7 +19563,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
